--- a/test-cases/textBox-test-cases.xlsx
+++ b/test-cases/textBox-test-cases.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="17329"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hristo.tentchev.OFFICE-SF\Desktop\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hasha\OneDrive\Desktop\playwright-pytest-framework\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5278D1-00A1-49BE-B7D7-530EEDB8FF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC001" sheetId="1" r:id="rId1"/>
@@ -19,26 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
   <si>
     <t>Test steps</t>
   </si>
   <si>
-    <t>Test ID</t>
-  </si>
-  <si>
     <t>Expected Outcome</t>
   </si>
   <si>
-    <t>Test module</t>
-  </si>
-  <si>
-    <t>Navigate to https://demoqa.com/text-box</t>
-  </si>
-  <si>
-    <t>Navigate to demoqa.com-text-box page</t>
-  </si>
-  <si>
     <t>Test case ID</t>
   </si>
   <si>
@@ -60,63 +49,9 @@
     <t>DemoQA - TextBox page</t>
   </si>
   <si>
-    <t xml:space="preserve">Need to navigate to </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="false"/>
-        <i val="false"/>
-        <u val="none"/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-      </rPr>
-      <t xml:space="preserve">Need to navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i val="false"/>
-        <u val="none"/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-      </rPr>
-      <t>demoqa.com-text-box page</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="false"/>
-        <i val="false"/>
-        <u val="none"/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-      </rPr>
-      <t xml:space="preserve">Need to navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i val="false"/>
-        <u val="none"/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-      </rPr>
-      <t>demoqa.com-text-box page</t>
-    </r>
-  </si>
-  <si>
     <t>Need to navigated to demoqa.com-text-box page</t>
   </si>
   <si>
-    <t>Test environment</t>
-  </si>
-  <si>
     <t>Test browser</t>
   </si>
   <si>
@@ -126,132 +61,30 @@
     <t>Need internet connection</t>
   </si>
   <si>
-    <t>Input the full name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filled with the full name </t>
-  </si>
-  <si>
-    <t>Check fullname text box</t>
-  </si>
-  <si>
     <t>low</t>
   </si>
   <si>
     <t>Test Data</t>
   </si>
   <si>
-    <t>Any meaningful name</t>
-  </si>
-  <si>
     <t>Positive</t>
   </si>
   <si>
     <t>TC-TextBox-001</t>
   </si>
   <si>
-    <t>Check email text box</t>
-  </si>
-  <si>
-    <t>Check currentAddress text box</t>
-  </si>
-  <si>
-    <t>Check permant text box</t>
-  </si>
-  <si>
-    <t>Check Full Name text box</t>
-  </si>
-  <si>
-    <t>Check Email text box</t>
-  </si>
-  <si>
-    <t>Check Current Address text box</t>
-  </si>
-  <si>
-    <t>Check Permant Address text box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check TextBox form submission with valid data input </t>
-  </si>
-  <si>
-    <t>Input the Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check TextBox form submission with all valid data input </t>
-  </si>
-  <si>
     <t>Check TextBox form submission with all valid data</t>
   </si>
   <si>
-    <t>Input the Current Address</t>
-  </si>
-  <si>
-    <t>Input the Permanant Address</t>
-  </si>
-  <si>
-    <t>Input the Permanent Address</t>
-  </si>
-  <si>
-    <t>Any meaningful Email</t>
-  </si>
-  <si>
-    <t>Any valid Email</t>
-  </si>
-  <si>
-    <t>Any meaningful name - John Doe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any valid Email - </t>
-  </si>
-  <si>
-    <t>Any valid name - John Doe</t>
-  </si>
-  <si>
-    <t>Any valid Email - john.doe@example.com</t>
-  </si>
-  <si>
-    <t>Any valid address - 123 Main St</t>
-  </si>
-  <si>
-    <t>Any valid address - 456 Oak Ave</t>
-  </si>
-  <si>
-    <t>Filled with the email</t>
-  </si>
-  <si>
-    <t>Filled with the address</t>
-  </si>
-  <si>
     <t>Click submit button</t>
   </si>
   <si>
-    <t>Entered data should be shown in the text box</t>
-  </si>
-  <si>
-    <t>Entered data should be shown in the text box.</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Input the Full name, Email, Current Address, Permanent Address</t>
-  </si>
-  <si>
     <t>John Doe</t>
   </si>
   <si>
-    <t xml:space="preserve">John Doe, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Doe, john.doe@example.com, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any valid address - </t>
-  </si>
-  <si>
-    <t>John Doe, john.doe@example.com, 123 Main St</t>
-  </si>
-  <si>
     <t>John Doe, john.doe@example.com, 123 Main St, 456 Oak Ave</t>
   </si>
   <si>
@@ -261,30 +94,15 @@
     <t>Filled the valid data into text boxes</t>
   </si>
   <si>
-    <t xml:space="preserve">Input data shown line by line in the textbox </t>
-  </si>
-  <si>
     <t>TC-TextBox-002</t>
   </si>
   <si>
-    <t>Check TextBox form submission with all valid data except invalid email</t>
-  </si>
-  <si>
     <t>Input valid data into form except email (Full name, Invalid Email, Current Address, Permanent Address)</t>
   </si>
   <si>
     <t>John Doe, john.doe-example.com, 123 Main St, 456 Oak Ave</t>
   </si>
   <si>
-    <t xml:space="preserve">Input data will not shown line by line in the textbox </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input data will not shown in the textbox </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email text box border is getting red and showing error when </t>
-  </si>
-  <si>
     <t>Check TextBox form submission with all valid data except email</t>
   </si>
   <si>
@@ -294,15 +112,6 @@
     <t>Negative</t>
   </si>
   <si>
-    <t>Email text box border is getting red and showing relevant error when hovering on the email-textbox</t>
-  </si>
-  <si>
-    <t>Email text box border is getting red and showing relevant error when hovering on the email-textbox. No data showing in the textbox.</t>
-  </si>
-  <si>
-    <t>Email text box border is getting red and showing relevant error when hovering on the email-textbox &amp; No data showing in the textbox</t>
-  </si>
-  <si>
     <t>TC-TextBox-003</t>
   </si>
   <si>
@@ -327,26 +136,23 @@
     <t>Empty text boxes except Full Name text box</t>
   </si>
   <si>
-    <t>Only filled data showing in the textbox</t>
-  </si>
-  <si>
-    <t>Only Full Name is showing in the textbox</t>
-  </si>
-  <si>
     <t>Email text box border is getting red and showing relevant error when hovering on the email-textbox &amp; No data is showing in the textbox</t>
   </si>
   <si>
-    <t>No data showing in the textbox</t>
-  </si>
-  <si>
-    <t>No diffrence is happening</t>
+    <t>Only Full Name is showing with front text in text area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input data shown line by line with front texts in the textbox </t>
+  </si>
+  <si>
+    <t>No texts showing in textarea</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -355,21 +161,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -394,44 +189,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment vertical="top" horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment vertical="top" horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment vertical="top" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment wrapText="1" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment wrapText="1" vertical="top" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment wrapText="1" vertical="top" horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
-      <alignment wrapText="1" horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -746,249 +535,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.453125" customWidth="1"/>
     <col min="3" max="3" width="28.54296875" customWidth="1"/>
     <col min="4" max="4" width="30.26953125" customWidth="1"/>
-    <col min="5" max="5" width="26.08984375" customWidth="1" style="8"/>
+    <col min="5" max="5" width="26.08984375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="10"/>
+      <c r="B3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customFormat="1" s="6">
-      <c r="A7" s="11" t="s">
-        <v>28</v>
-      </c>
       <c r="B7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="11"/>
-      <c r="C9" s="8"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" ht="55.5">
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="7"/>
+      <c r="C9" s="5"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" ht="69">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="13" ht="28.5">
+      <c r="C11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" ht="28.5">
+        <v>35</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="16">
+      <c r="C14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>31</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
-      <c r="C17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="C17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="F7:F8"/>
@@ -997,14 +789,11 @@
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
